--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_086_Chagos_Archipelago_UK.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_086_Chagos_Archipelago_UK.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra5653ec7d5234379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R899ecfcb9ebf4554"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb474836467da4d6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rbe7d771a5947445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R0c31c28cd5ad408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rdca20d1339a2455f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra75beeb6126d4363"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R27a8f6431fdf4c11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rbd8e3cb5d487483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9a97afb4d84a4232"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re2f862701ac64d88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R01383508ab1c4559"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ086CommercialTable" displayName="EEZ086CommercialTable" ref="A1:O5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O5"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ086CommercialTable" displayName="EEZ086CommercialTable" ref="A1:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E5"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ086FunctionalTable" displayName="EEZ086FunctionalTable" ref="A1:O7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O7"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ086FunctionalTable" displayName="EEZ086FunctionalTable" ref="A1:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E7"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ086ValidationTable" displayName="EEZ086ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ086ValidationTable" displayName="EEZ086ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -2168,7 +2122,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R860f21b5bc44470b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfa39444aa7141f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2178,20 +2132,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -2199,282 +2143,98 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>16.3638533112</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.287681504696633</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>193.94630263968108</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>16.3638533112</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>194.2031310621532</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$23,A2,'Species'!$U$2:$U$23))</x:f>
-        <x:v>3177.9115492768233</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.287681504696633</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>193.94630263968108</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>3173.7088466453424</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>4.202702631480861</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0013242243805456</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00132422438054555</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>52.489898872400005</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.128629359882386</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1344.7122458875072</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>52.489898872400005</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1392.9206294478124</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$23,A3,'Species'!$U$2:$U$23))</x:f>
-        <x:v>73114.26297699544</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.128629359882386</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1344.7122458875072</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>70583.80979911314</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>2530.4531778823</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0358503343059005</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.03585033430590048</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.4862236768000001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.35046894691215</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2241.1397932303803</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.4862236768000001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2247.5517788636353</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$23,A4,'Species'!$U$2:$U$23))</x:f>
-        <x:v>3340.3646685810927</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.35046894691215</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2241.1397932303803</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3330.835023717648</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>9.5296448634449</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0028610377864973</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.002861037786497324</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>64.9089997722</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.4480603143367965</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2805.8232805251187</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>64.9089997722</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2825.38965797811</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$23,A5,'Species'!$U$2:$U$23))</x:f>
-        <x:v>183393.21666607738</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.4480603143367965</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2805.8232805251187</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>182123.1826764384</x:v>
       </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1270.0339896389924</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0069734888824964</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0069734888824963355</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G5">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O5">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63b68c615fe44728"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4c1d01627c2457e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2484,20 +2244,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -2505,390 +2255,136 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>69.90964167240001</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.434609355983699</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2720.2533636315306</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>69.90964167240001</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2753.4574790428096</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$23,A2,'Species'!$U$2:$U$23))</x:f>
-        <x:v>192493.2257200727</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.434609355983699</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2720.2533636315306</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>190171.93790962116</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2321.2878104515257</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0122062583784297</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.012206258378429698</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.0031575438</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.61</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>407.3802778041126</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.0031575438</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$23,A3,'Species'!$U$2:$U$23))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1.2863210704226533</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.61</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1.2863210704226533</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1.4830661330000001</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.352045453232663</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2249.290004064963</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1.4830661330000001</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2251.469623108621</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$23,A4,'Species'!$U$2:$U$23))</x:f>
-        <x:v>3339.07834751067</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.352045453232663</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2249.290004064963</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3335.845828324179</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>3.2325191864911176</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0009690253545425</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0009690253545425481</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>14.5681530817</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.28</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>190.54607179632464</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>14.5681530817</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$23,A5,'Species'!$U$2:$U$23))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2775.9043430454562</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.28</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>2775.9043430454562</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>37.113427952</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.114261063168551</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1300.951371130626</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>37.113427952</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1404.6455486316427</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$23,A6,'Species'!$U$2:$U$23))</x:f>
-        <x:v>52131.211367237986</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.114261063168551</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1300.951371130626</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>48282.764981512104</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>3848.4463857258816</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0797064208563756</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.07970642085637568</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>12.1715292497</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.003588678421413</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1008.297472214894</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>12.1715292497</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1009.3267255054494</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$23,A7,'Species'!$U$2:$U$23))</x:f>
-        <x:v>12285.049761993501</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.003588678421413</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1008.297472214894</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>12272.522175462156</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>12.52758653134515</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0010207833689144</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.001020783368914417</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G7">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O7">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11c0e2e01c7e4cbc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcee4bbcf2dc74251"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3063,7 +2559,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -3162,7 +2658,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>263025.7558609307</x:v>
+        <x:v>259211.53634591453</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -3176,7 +2672,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>263025.7558609307</x:v>
+        <x:v>256840.26155903548</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -3190,7 +2686,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>5.820766091346741e-11</x:v>
+        <x:v>-3814.219515016128</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -3204,7 +2700,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>5.820766091346741e-11</x:v>
+        <x:v>-6185.494301895174</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -3215,9 +2711,9 @@
         <x:v>EEZ_086</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -3229,47 +2725,19 @@
         <x:v>EEZ_086</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_086</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_086</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc35b8db2e61b4e2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e047b56ed6d4366"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3316,7 +2784,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
